--- a/data/file_generation/reference/data_221/2025-2026学年上学期七年级7班学生_res.xlsx
+++ b/data/file_generation/reference/data_221/2025-2026学年上学期七年级7班学生_res.xlsx
@@ -12006,18 +12006,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CBCF886-4E58-4B2B-8C12-ACC5FF11AEB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C957FA8-6B8E-4213-A8E4-52E358621899}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F380AA-CE58-4DF5-9566-E76A5527CC84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F962D2-63C8-44CE-9263-3F66DEF74C8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEABEEE-B852-4202-8828-543CACDF4563}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74533E72-E680-46CB-B560-FE5983171216}"/>
 </file>